--- a/data/trans_camb/P6902-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 23,54</t>
+          <t>-7,75; 23,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 32,7</t>
+          <t>-0,15; 31,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 44,99</t>
+          <t>3,55; 45,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 45,19</t>
+          <t>3,15; 47,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 26,52</t>
+          <t>-21,12; 27,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 40,34</t>
+          <t>-9,85; 43,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 27,01</t>
+          <t>2,83; 28,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 25,47</t>
+          <t>-0,16; 25,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 38,16</t>
+          <t>4,07; 36,56</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 117,58</t>
+          <t>-26,6; 115,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 165,17</t>
+          <t>-1,55; 151,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 212,5</t>
+          <t>11,69; 215,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 298,43</t>
+          <t>7,25; 305,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 156,17</t>
+          <t>-63,85; 161,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 224,0</t>
+          <t>-22,87; 261,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 126,58</t>
+          <t>10,26; 138,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 113,34</t>
+          <t>-1,0; 120,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 180,54</t>
+          <t>16,88; 165,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 13,2</t>
+          <t>-5,49; 12,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 4,04</t>
+          <t>-13,79; 4,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 23,11</t>
+          <t>4,79; 22,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 17,72</t>
+          <t>-8,45; 16,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 21,33</t>
+          <t>-3,1; 22,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 15,01</t>
+          <t>-19,19; 15,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 11,88</t>
+          <t>-3,52; 11,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 8,47</t>
+          <t>-6,73; 7,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 17,72</t>
+          <t>-2,75; 18,04</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 35,41</t>
+          <t>-12,28; 34,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 11,25</t>
+          <t>-30,88; 11,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 62,23</t>
+          <t>10,32; 59,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 42,7</t>
+          <t>-15,35; 40,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 49,65</t>
+          <t>-5,62; 52,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 32,76</t>
+          <t>-33,82; 34,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 30,0</t>
+          <t>-7,07; 29,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 20,8</t>
+          <t>-14,36; 19,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 43,8</t>
+          <t>-5,47; 44,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 9,74</t>
+          <t>-22,77; 11,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 5,67</t>
+          <t>-26,18; 6,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 22,88</t>
+          <t>-4,11; 24,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 19,43</t>
+          <t>-16,42; 21,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 19,43</t>
+          <t>-11,35; 19,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 31,78</t>
+          <t>6,77; 32,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 9,87</t>
+          <t>-14,22; 11,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 7,76</t>
+          <t>-15,15; 8,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 23,56</t>
+          <t>4,97; 23,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 13,48</t>
+          <t>-28,51; 16,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 7,85</t>
+          <t>-31,75; 9,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 34,26</t>
+          <t>-4,45; 36,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 31,62</t>
+          <t>-20,7; 36,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 32,4</t>
+          <t>-14,82; 31,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,85; 56,54</t>
+          <t>8,34; 58,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 14,66</t>
+          <t>-17,88; 16,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 11,22</t>
+          <t>-19,72; 11,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,59; 35,29</t>
+          <t>6,42; 36,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 10,98</t>
+          <t>-3,62; 10,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 6,76</t>
+          <t>-7,72; 6,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,34; 26,12</t>
+          <t>10,72; 25,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 15,3</t>
+          <t>-3,92; 16,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 18,09</t>
+          <t>-0,21; 19,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 19,68</t>
+          <t>-8,56; 19,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 11,01</t>
+          <t>-0,38; 10,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,71</t>
+          <t>-1,37; 10,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 21,2</t>
+          <t>5,35; 21,14</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 27,71</t>
+          <t>-8,03; 27,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 16,34</t>
+          <t>-16,67; 16,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,24; 64,67</t>
+          <t>22,82; 63,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 33,11</t>
+          <t>-6,75; 34,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 39,78</t>
+          <t>-0,39; 41,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 41,77</t>
+          <t>-13,76; 40,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 25,2</t>
+          <t>-0,76; 24,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 22,5</t>
+          <t>-2,83; 23,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 48,0</t>
+          <t>12,18; 48,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6902-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6902-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,05</t>
+          <t>22,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,55</t>
+          <t>25,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21,63</t>
+          <t>23,76</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 23,05</t>
+          <t>-5,78; 23,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 31,43</t>
+          <t>-0,1; 32,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 45,01</t>
+          <t>3,75; 43,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 47,19</t>
+          <t>2,05; 44,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 27,75</t>
+          <t>-23,6; 28,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 43,27</t>
+          <t>3,93; 45,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 28,58</t>
+          <t>2,37; 26,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 25,89</t>
+          <t>-2,24; 24,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 36,56</t>
+          <t>8,7; 37,08</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 115,91</t>
+          <t>-20,39; 110,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 151,68</t>
+          <t>-0,62; 159,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 215,38</t>
+          <t>9,14; 200,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 305,1</t>
+          <t>5,3; 294,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,85; 161,11</t>
+          <t>-69,13; 187,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 261,58</t>
+          <t>10,34; 292,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 138,49</t>
+          <t>6,76; 119,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 120,45</t>
+          <t>-7,68; 107,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,88; 165,96</t>
+          <t>28,95; 170,38</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>14,2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>11,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>14,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 12,99</t>
+          <t>-5,83; 13,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 4,12</t>
+          <t>-12,95; 4,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 22,6</t>
+          <t>5,11; 22,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 16,59</t>
+          <t>-8,01; 17,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 22,39</t>
+          <t>-3,93; 22,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 15,5</t>
+          <t>0,89; 22,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 11,91</t>
+          <t>-3,31; 12,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 7,9</t>
+          <t>-6,27; 8,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 18,04</t>
+          <t>6,68; 20,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 34,31</t>
+          <t>-12,61; 35,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 11,09</t>
+          <t>-29,43; 11,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,32; 59,88</t>
+          <t>11,58; 62,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 40,23</t>
+          <t>-14,33; 40,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 52,23</t>
+          <t>-6,61; 50,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 34,21</t>
+          <t>1,78; 56,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 29,81</t>
+          <t>-7,38; 29,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 19,59</t>
+          <t>-13,44; 20,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 44,93</t>
+          <t>13,49; 51,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>10,85</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,41</t>
+          <t>17,66</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,93</t>
+          <t>13,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 11,73</t>
+          <t>-21,95; 11,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 6,41</t>
+          <t>-23,94; 5,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 24,07</t>
+          <t>-1,73; 23,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 21,84</t>
+          <t>-15,73; 19,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 19,05</t>
+          <t>-12,73; 17,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 32,63</t>
+          <t>5,7; 30,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 11,09</t>
+          <t>-13,93; 11,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 8,04</t>
+          <t>-14,41; 7,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 23,7</t>
+          <t>4,7; 23,55</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 16,1</t>
+          <t>-26,87; 15,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 9,11</t>
+          <t>-29,2; 7,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 36,19</t>
+          <t>-1,96; 35,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 36,24</t>
+          <t>-20,44; 30,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 31,97</t>
+          <t>-16,86; 29,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 58,31</t>
+          <t>6,97; 53,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 16,28</t>
+          <t>-17,82; 16,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 11,62</t>
+          <t>-18,54; 10,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 36,47</t>
+          <t>5,94; 35,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18,29</t>
+          <t>18,07</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,19</t>
+          <t>16,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,17</t>
+          <t>18,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 10,87</t>
+          <t>-3,62; 11,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 6,7</t>
+          <t>-7,76; 7,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 25,54</t>
+          <t>10,49; 24,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 16,13</t>
+          <t>-4,02; 15,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 19,33</t>
+          <t>-0,47; 18,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 19,06</t>
+          <t>7,74; 24,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 10,67</t>
+          <t>-0,34; 11,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 10,01</t>
+          <t>-1,57; 9,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 21,14</t>
+          <t>13,04; 23,83</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 27,43</t>
+          <t>-7,67; 27,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 16,41</t>
+          <t>-16,75; 17,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,82; 63,0</t>
+          <t>22,63; 61,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 34,81</t>
+          <t>-7,05; 34,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 41,95</t>
+          <t>-0,81; 40,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 40,29</t>
+          <t>13,97; 53,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 24,64</t>
+          <t>-0,88; 25,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 23,35</t>
+          <t>-3,31; 23,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,18; 48,67</t>
+          <t>26,99; 55,62</t>
         </is>
       </c>
     </row>
